--- a/artfynd/A 4801-2019 artfynd.xlsx
+++ b/artfynd/A 4801-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,6 +1735,114 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1660890</v>
+      </c>
+      <c r="B11" t="n">
+        <v>89745</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ej möjlig att validera</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5745</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gyllenfingersvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramaria brunneicontusa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lundagård objekt 32, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>667247</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6616244</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2010-09-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2010-10-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Från : IINVENTERING AV SVAMPAR I ÅSBARRSKOGAR PÅ SWEDAVIAS MARKINNEHAV VID ARLANDA. Ekologigruppen ab 2010</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Via Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4801-2019 artfynd.xlsx
+++ b/artfynd/A 4801-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
